--- a/reports/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/reports/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T10:57:52+00:00</t>
+          <t>2026-06-09T16:55:07+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/reports/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:07+00:00</t>
+          <t>2026-06-09T22:25:18+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/reports/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:18+00:00</t>
+          <t>2026-06-09T23:12:24+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/reports/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:24+00:00</t>
+          <t>2026-06-10T10:52:04+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/reports/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:04+00:00</t>
+          <t>2026-07-03T07:03:01+00:00</t>
         </is>
       </c>
     </row>
